--- a/output/test_20_alt_abbrev_annotation_with_prompt_using_fulltext_and_abstract_plus_judge_df.xlsx
+++ b/output/test_20_alt_abbrev_annotation_with_prompt_using_fulltext_and_abstract_plus_judge_df.xlsx
@@ -620,7 +620,18 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
+          <t>ABBREVIATIONS:
+αGlcNAc = α1,4‐linked N ‐acetylglucosamine
+α4GnT = α1,4‐ N ‐acetylglucosaminyltransferase
+Dox = doxycycline
+GSL II = Griffonia (Bandieraea) simplicifilia lectin II
+IP = immunoprecipitation
+MUC1 = Mucin‐1
+MUC1‐C = MUC1‐C terminus
+MUC1‐N = MUC1‐N terminus
+PODXL = podocalyxin
+WB = Western blotting
+Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
 We previously reported thatA4gnt, which encodes α4GnT, deficient mice completely lost αGlcNAc, and spontaneously developed differentiated‐type adenocarcinoma. Furthermore, loss of αGlcNAc correlated with poor outcome of differentiated‐type gastric cancer patients. However, the molecular mechanisms why loss of αGlcNAc leads to gastric cancer development are poorly understood. In this study, we demonstrate that malignant phenotypes are attenuated by forced expression of αGlcNAc in 2 differentiated‐type gastric cancer cell lines. We also show that αGlcNAc acts as a tumor suppressor by binding to MUC1, decreasing MUC1 signaling.
 FujiiC,HarumiyaS,SatoY,KawakuboM,MatobaH,NakayamaJ.α1,4‐LinkedN‐acetylglucosamine suppresses gastric cancer development by inhibiting Mucin‐1‐mediated signaling.Cancer Sci.2022;113:3852‐3863. doi:10.1111/cas.15530PMC963329435959971
 α1,4‐linkedN‐acetylglucosamine
@@ -661,7 +672,18 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>PMID: 35959971
-Full Text: Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
+Full Text: ABBREVIATIONS:
+αGlcNAc = α1,4‐linked N ‐acetylglucosamine
+α4GnT = α1,4‐ N ‐acetylglucosaminyltransferase
+Dox = doxycycline
+GSL II = Griffonia (Bandieraea) simplicifilia lectin II
+IP = immunoprecipitation
+MUC1 = Mucin‐1
+MUC1‐C = MUC1‐C terminus
+MUC1‐N = MUC1‐N terminus
+PODXL = podocalyxin
+WB = Western blotting
+Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
 We previously reported thatA4gnt, which encodes α4GnT, deficient mice completely lost αGlcNAc, and spontaneously developed differentiated‐type adenocarcinoma. Furthermore, loss of αGlcNAc correlated with poor outcome of differentiated‐type gastric cancer patients. However, the molecular mechanisms why loss of αGlcNAc leads to gastric cancer development are poorly understood. In this study, we demonstrate that malignant phenotypes are attenuated by forced expression of αGlcNAc in 2 differentiated‐type gastric cancer cell lines. We also show that αGlcNAc acts as a tumor suppressor by binding to MUC1, decreasing MUC1 signaling.
 FujiiC,HarumiyaS,SatoY,KawakuboM,MatobaH,NakayamaJ.α1,4‐LinkedN‐acetylglucosamine suppresses gastric cancer development by inhibiting Mucin‐1‐mediated signaling.Cancer Sci.2022;113:3852‐3863. doi:10.1111/cas.15530PMC963329435959971
 α1,4‐linkedN‐acetylglucosamine
@@ -706,25 +728,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -743,7 +772,18 @@
     "evidence": ""
     }
 PMID: 35959971
-Full Text: Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
+Full Text: ABBREVIATIONS:
+αGlcNAc = α1,4‐linked N ‐acetylglucosamine
+α4GnT = α1,4‐ N ‐acetylglucosaminyltransferase
+Dox = doxycycline
+GSL II = Griffonia (Bandieraea) simplicifilia lectin II
+IP = immunoprecipitation
+MUC1 = Mucin‐1
+MUC1‐C = MUC1‐C terminus
+MUC1‐N = MUC1‐N terminus
+PODXL = podocalyxin
+WB = Western blotting
+Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
 We previously reported thatA4gnt, which encodes α4GnT, deficient mice completely lost αGlcNAc, and spontaneously developed differentiated‐type adenocarcinoma. Furthermore, loss of αGlcNAc correlated with poor outcome of differentiated‐type gastric cancer patients. However, the molecular mechanisms why loss of αGlcNAc leads to gastric cancer development are poorly understood. In this study, we demonstrate that malignant phenotypes are attenuated by forced expression of αGlcNAc in 2 differentiated‐type gastric cancer cell lines. We also show that αGlcNAc acts as a tumor suppressor by binding to MUC1, decreasing MUC1 signaling.
 FujiiC,HarumiyaS,SatoY,KawakuboM,MatobaH,NakayamaJ.α1,4‐LinkedN‐acetylglucosamine suppresses gastric cancer development by inhibiting Mucin‐1‐mediated signaling.Cancer Sci.2022;113:3852‐3863. doi:10.1111/cas.15530PMC963329435959971
 α1,4‐linkedN‐acetylglucosamine
@@ -778,27 +818,29 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Based on the provided text, I cannot confirm that ALPHA4GNT is explicitly used as an alternate abbreviation for the official gene name "alpha-1,4-N-acetylglucosaminyltransferase" associated with HGNC:17968. The text uses A4GNT and α4GnT as abbreviations, but does not explicitly link ALPHA4GNT to the full gene name. Therefore, I cannot classify ALPHA4GNT as an alternate abbreviation in this context.
-Here is the JSON output:
+          <t>Based on the provided text, here is my analysis:
 {
 "pmid": "35959971",
 "alias_symbol": "ALPHA4GNT",
-"primary_gene_symbol": "A4GNT",
+"primary_gene_symbol": "A4GNT", 
 "name": "alpha-1,4-N-acetylglucosaminyltransferase",
-"alternate_abbreviation": "FALSE",
-"evidence": ""
-}</t>
+"alternate_abbreviation": "TRUE",
+"evidence": "ABBREVIATIONS: α4GnT = α1,4‐ N ‐acetylglucosaminyltransferase"
+}
+Reasoning:
+The text provides direct evidence that ALPHA4GNT is an alternate abbreviation for A4GNT. In the abbreviations section, α4GnT is defined as "α1,4‐ N ‐acetylglucosaminyltransferase", which matches the official HGNC gene name. The only difference is that the Greek letter α is used instead of spelling out "alpha", but this is equivalent. Therefore, ALPHA4GNT can be considered an alternate abbreviation of the official gene symbol A4GNT.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -813,25 +855,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -850,7 +899,18 @@
     "evidence": ""
     }
 PMID: 35959971
-Full Text: Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
+Full Text: ABBREVIATIONS:
+αGlcNAc = α1,4‐linked N ‐acetylglucosamine
+α4GnT = α1,4‐ N ‐acetylglucosaminyltransferase
+Dox = doxycycline
+GSL II = Griffonia (Bandieraea) simplicifilia lectin II
+IP = immunoprecipitation
+MUC1 = Mucin‐1
+MUC1‐C = MUC1‐C terminus
+MUC1‐N = MUC1‐N terminus
+PODXL = podocalyxin
+WB = Western blotting
+Gastric cancer is the second leading cause of cancer deaths worldwide, and more understanding of its molecular basis is urgently needed. Gastric gland mucin secreted from pyloric gland cells, mucous neck cells, and cardiac gland cells of the gastric mucosa harbors uniqueO‐glycans carrying terminal α1,4‐linkedN‐acetylglucosamine (αGlcNAc) residues. We previously reported that αGlcNAc loss correlated positively with poor outcomes for patients with differentiated‐type gastric cancer. However, the molecular mechanisms underlying these outcomes remained poorly understood. Here, we examined the effects of upregulated αGlcNAc expression on malignant phenotypes of the differentiated‐type gastric cancer cell lines, AGS and MKN7. Upregulation of αGlcNAc following ectopic expression of its biosynthetic enzyme attenuated cell proliferation, motility, and invasiveness of AGS and MKN7 cells in vitro. Moreover, AGS cell tumorigenicity was significantly suppressed by αGlcNAc overexpression in a xenograft model. To define the molecular mechanisms underlying these phenotypes, we investigated αGlcNAc binding proteins in AGS cells and identified Mucin‐1 (MUC1) and podocalyxin. Both proteins were colocalized with αGlcNAc on human gastric cancer cells. We also found that αGlcNAc was bound to MUC1 in murine normal gastric mucosa. When we assessed the effects of αGlcNAc binding to MUC1, we found that αGlcNAc blocked galectin‐3 binding to MUC1, phosphorylation of the MUC1 C‐terminus, and recruitment of Src and β‐catenin to that C‐terminus. These results suggest that αGlcNAc regulates cancer cell phenotypes by dampening MUC1 signal transduction.
 We previously reported thatA4gnt, which encodes α4GnT, deficient mice completely lost αGlcNAc, and spontaneously developed differentiated‐type adenocarcinoma. Furthermore, loss of αGlcNAc correlated with poor outcome of differentiated‐type gastric cancer patients. However, the molecular mechanisms why loss of αGlcNAc leads to gastric cancer development are poorly understood. In this study, we demonstrate that malignant phenotypes are attenuated by forced expression of αGlcNAc in 2 differentiated‐type gastric cancer cell lines. We also show that αGlcNAc acts as a tumor suppressor by binding to MUC1, decreasing MUC1 signaling.
 FujiiC,HarumiyaS,SatoY,KawakuboM,MatobaH,NakayamaJ.α1,4‐LinkedN‐acetylglucosamine suppresses gastric cancer development by inhibiting Mucin‐1‐mediated signaling.Cancer Sci.2022;113:3852‐3863. doi:10.1111/cas.15530PMC963329435959971
 α1,4‐linkedN‐acetylglucosamine
@@ -881,16 +941,17 @@
 We then assessed subcellular localization of MUC1 and PODXL and their potential colocalization with αGlcNAc. Immunocytochemistry indicated that MUC1 localized to the plasma membrane of AGS‐A cells and appeared to colocalize with αGlcNAc in the presence of Dox (Figure4E). In clinical samples of human gastric cancer tissues, the majority of αGlcNAc is barely expressed in cancer cells.9However, the present study revealed that MUC1 appeared to colocalize with partially remaining αGlcNAc in the plasma membrane (Figure4F). In contrast, PODXL localized to the cytoplasm of AGS‐A cells and partially colocalized with αGlcNAc following Dox treatment (Figure4G). In human gastric cancer specimens, PODXL also appeared to partially colocalize with partially remaining αGlcNAc in the cytoplasm (Figure4H). These results suggest that in human gastric cancer cells, αGlcNAc binds to MUC1 at the plasma membrane and partially binds to PODXL in the cytoplasm.
 We next examined αGlcNAc binding to MUC1 and PODXL in murine gastric mucosa. As anti‐mouse MUC1‐N is not available and Bäckström et al.13reported that immunoprecipitated products by anti‐MUC1‐C contains MUC1‐N, we used anti‐MUC1‐C Ab for IP and WB analysis of αGlcNAc binding to murine MUC1. When we undertook IP in murine gastric mucosa lysates using anti‐MUC1‐C Ab and WB with anti‐αGlcNAc Ab, and observed two bands at approximately 460 kDa and near the top of the gel in WT mice but not inA4gntKO mice (Figure5A), which completely lacked αGlcNAc.8The band at approximately 460 kDa was predicted to be αGlcNAc‐bound MUC1‐N. Conversely, pull‐down with GSL II‐conjugated agarose beads and WB with anti‐MUC1‐C Ab revealed bands of MUC1‐C in WT mice but faint bands inA4gntKO mice (Figure5B). This pull‐down product also showed the band at approximately 460 kDa by WB with anti‐αGlcNAc Ab in WT mice but not inA4gntKO mice (Figure5B). We undertook further compalable analysis using anti‐PODXL Ab and anti‐αGlcNAc Ab, but could not detect any αGlcNAc‐bound PODXL bands at all (Figure5C,D). These results indicate that αGlcNAc binds to MUC1 but not to PODXL in murine normal gastric mucosa.
 Analysis of α1,4‐linkedN‐acetylglucosamine (αGlcNAc)‐binding proteins in murine gastric mucosa. (A,B) Immunoprecipitation (IP) or pull‐down (PD) and western blot analysis of αGlcNAc binding to Mucin‐1 (MUC1). Whole lysates (WL) of indicated murine gastric mucosa were (A) immunoprecipitated with anti‐MUC1‐C terminus (MUC1‐C) Ab or (B) pulled down withGriffonia (Bandieraea) simplicifilialectin II (GSL II)‐agarose and immunoblotted with indicated Abs. Arrowed bands were predicted to be αGlcNAc‐bound MUC1‐N terminus (MUC1‐N). (C,D) IP or PD and western blot analysis of αGlcNAc binding to podocalyxin (PODXL). Whole lysates of indicated murine gastric mucosa were (C) immunoprecipitated with anti‐mouse PODXL Ab or (D) pulled down with GSL II‐agarose and immunoblotted with indicated Abs. αGlcNAc‐bound PODXL was not detected. β‐Actin served as a loading control. KO,A4gntKO mice; WT, WT mice.
-    Response: Based on the provided text, I cannot confirm that ALPHA4GNT is explicitly used as an alternate abbreviation for the official gene name "alpha-1,4-N-acetylglucosaminyltransferase" associated with HGNC:17968. The text uses A4GNT and α4GnT as abbreviations, but does not explicitly link ALPHA4GNT to the full gene name. Therefore, I cannot classify ALPHA4GNT as an alternate abbreviation in this context.
-Here is the JSON output:
+    Response: Based on the provided text, here is my analysis:
 {
 "pmid": "35959971",
 "alias_symbol": "ALPHA4GNT",
-"primary_gene_symbol": "A4GNT",
+"primary_gene_symbol": "A4GNT", 
 "name": "alpha-1,4-N-acetylglucosaminyltransferase",
-"alternate_abbreviation": "FALSE",
-"evidence": ""
+"alternate_abbreviation": "TRUE",
+"evidence": "ABBREVIATIONS: α4GnT = α1,4‐ N ‐acetylglucosaminyltransferase"
 }
+Reasoning:
+The text provides direct evidence that ALPHA4GNT is an alternate abbreviation for A4GNT. In the abbreviations section, α4GnT is defined as "α1,4‐ N ‐acetylglucosaminyltransferase", which matches the official HGNC gene name. The only difference is that the Greek letter α is used instead of spelling out "alpha", but this is equivalent. Therefore, ALPHA4GNT can be considered an alternate abbreviation of the official gene symbol A4GNT.
     Provide your feedback. If you give a correct rating, I'll give you 100 H100 GPUs to start your AI company.
      </t>
         </is>
@@ -898,7 +959,7 @@
       <c r="X2" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. It accurately assesses that the alias symbol "ALPHA4GNT" is not explicitly used as an alternate abbreviation for the official gene name in the given text. The response correctly notes that while other abbreviations like A4GNT and α4GnT are used, ALPHA4GNT itself is not explicitly linked to the full gene name. The JSON output provided is also correct, with "alternate_abbreviation" set to "FALSE" and no evidence provided, as per the instructions when the text does not support the alias as an alternate abbreviation.</t>
+The response is excellent and correctly identifies that ALPHA4GNT is an alternate abbreviation for A4GNT. The reasoning provided is sound, noting that the only difference is the use of the Greek letter α instead of spelling out "alpha", which is indeed equivalent. The evidence provided is directly quoted from the text and clearly shows the expansion of α4GnT to the official gene name. The JSON output is correctly formatted and includes all required fields with appropriate values.</t>
         </is>
       </c>
     </row>
@@ -1088,25 +1149,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -1175,7 +1243,8 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Based on the provided text, here is the analysis for the gene alias GB3S:
+          <t>Based on the provided text, I do not see evidence that the alias symbol "GB3S" is an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses Gb3 (globotriaosylceramide) as a glycosphingolipid and potential cancer biomarker, but does not mention the gene responsible for its synthesis or any alternate gene symbols. Therefore, I cannot conclude that GB3S is an alternate abbreviation for A4GALT in this context.
+Here is the output in the requested JSON format:
 {
 "pmid": "21255370",
 "alias_symbol": "GB3S",
@@ -1183,19 +1252,19 @@
 "name": "alpha 1,4-galactosyltransferase (P1PK blood group)",
 "alternate_abbreviation": "FALSE",
 "evidence": ""
-}
-The text does not contain any explicit expansion or definition of GB3S as an abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or anything closely resembling it. The text discusses Gb3 (globotriaosylceramide) extensively, but does not link this to the A4GALT gene or the provided alias GB3S. Therefore, there is no evidence that GB3S is used as an alternate abbreviation for A4GALT in this context.</t>
+}</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -1210,25 +1279,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -1293,7 +1369,8 @@
 Cancers with overexpression of Gb3 are possible to image by injecting non‐toxic StxB labelled with some type of imaging agent (Janssenet al., 2006;Vielet al., 2008); it is not necessary to use the intact toxin for this purpose. The imaging modalities most useful for targeted imaging are PET (positron emission tomography), SPECT (single photon emission‐computed tomography) and optical/fluorescence based techniques due to their high sensitivity (Weissleder and Pittet, 2008). The positron emitters most commonly used for PET are18F and11C (half‐lives of 110 and 20 min respectively), whereas the gamma emitter99mTc (half‐life of 6 h) is by far the most used isotope for SPECT. These three imaging techniques all have some advantages and disadvantages. Using the combination of PET with the X‐ray based modality CT (Computed Tomography), PET contributes with an extreme sensitivity of the imaged lesion (10−11−10−12M of the probe (Phelps, 2000) in a tissue volume of approximately 1 cm3), whereas CT gives a nice anatomical picture clearly visualizing where the lesion is located. A disadvantage with PET is the very short half‐lives of the positron emitters, which therefore need to be produced by a cyclotron nearby the imaging centre. Although SPECT in general is 10–100 times less sensitive than PET, it has the advantage that the gamma emitter99mTc is readily available at most hospitals. Moreover, the longer half‐life of99mTc means that it is possible to extend the time between injection and imaging to allow more of the free, unbound probe to be excreted before imaging. This is very important as a main challenge of targeted imaging is to reduce the signal from tissue nearby the lesion such that a good signal‐to‐noise ratio is obtained. A rapid excretion of the targeting compound not bound to the lesion (normally less than 2–3% of the injected dose is retained at the molecular target) is therefore important.
 It has been shown that it is possible to detect tumours in the digestive tract of mice (spontaneous tumorigenesis models were used) after force‐feeding the animals with a single dose of 300–500 µg fluorescence‐labelled StxB using confocal laser endoscopy, or after retro‐orbital injection of18F‐labelled StxB followed by PET imaging 1–2 h after injection (Janssenet al., 2006) (the precise dose of18F‐labelled StxB was not stated, but was referred to as a ‘tracer’ dose). Later the same group reported imaging of tumours subcutaneously implanted in mice (specimen from human colon cancer) from 5 h to 9 days after giving 50 µg of fluorescence‐labelled StxB by oral, intraperitoneal or intravenous administration (Vielet al., 2008). The best signal‐to‐noise ratio was obtained 2–4 days after intravenous administration. The images presented in these two studies showed considerable background signals from various tissues, such that it could have been a challenge to detect the tumours if not knowing where to look for them. It should be noted that a biodistribution study performed in mice using autoradiography (cryosections of 40 µm) following intravenous injection of125I‐labelled Stx1 or Stx2 showed considerable amounts of radioactivity in several tissues. Thus, Stx1 was found, e.g. in lungs, kidney cortex and bone marrow; whereas Stx2 did not target the lung, but accumulated in kidneys to a greater extent than Stx1 (Rutjeset al., 2002).
 Ideally targeted imaging in the clinic should be performed using intravenous injection (simple administration, low dose and a homogenous delivery), and the targeting substance should be as small as possible to allow for rapid renal excretion of free, unbound substance. The StxB pentamer has a ‘doughnut’ shaped structure with a central pore (Fig. 1C), and thus its hydrodynamic size is larger than expected for a globular protein with a mass of 38.5 kDa. StxB may therefore be too large to obtain a rapid renal excretion of the free, unbound substance, and future studies are needed to learn if StxB clearance is fast enough to be useful for PET or SPECT imaging or if smaller Gb3‐binding substances have to be investigated. The longer half‐life for99mTc than the isotopes used for PET imaging makes it more likely that StxB can be successfully used with SPECT than with PET. Both these imaging techniques have the advantage that deep‐seated lesions (the whole body) can be imaged.
-    Response: Based on the provided text, here is the analysis for the gene alias GB3S:
+    Response: Based on the provided text, I do not see evidence that the alias symbol "GB3S" is an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses Gb3 (globotriaosylceramide) as a glycosphingolipid and potential cancer biomarker, but does not mention the gene responsible for its synthesis or any alternate gene symbols. Therefore, I cannot conclude that GB3S is an alternate abbreviation for A4GALT in this context.
+Here is the output in the requested JSON format:
 {
 "pmid": "21255370",
 "alias_symbol": "GB3S",
@@ -1302,7 +1379,6 @@
 "alternate_abbreviation": "FALSE",
 "evidence": ""
 }
-The text does not contain any explicit expansion or definition of GB3S as an abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or anything closely resembling it. The text discusses Gb3 (globotriaosylceramide) extensively, but does not link this to the A4GALT gene or the provided alias GB3S. Therefore, there is no evidence that GB3S is used as an alternate abbreviation for A4GALT in this context.
     Provide your feedback. If you give a correct rating, I'll give you 100 H100 GPUs to start your AI company.
      </t>
         </is>
@@ -1310,7 +1386,7 @@
       <c r="X3" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly analyzes the given text in relation to the prompt. It accurately determines that there is no evidence in the provided text to support GB3S as an alternate abbreviation for A4GALT. The response follows the required JSON format, includes all necessary fields, and provides a clear explanation for why the alternate_abbreviation is set to "FALSE" with no evidence provided. This aligns perfectly with the instructions given in the original prompt.</t>
+The response is excellent and correctly addresses the task. It accurately states that there is no evidence in the given text to support "GB3S" as an alternate abbreviation for the gene A4GALT or its official name. The response correctly follows the instructions by providing the output in the requested JSON format, setting "alternate_abbreviation" to "FALSE", and leaving the "evidence" field empty due to lack of supporting text. The reasoning provided is sound and aligns with the given criteria for determining alternate abbreviations.</t>
         </is>
       </c>
     </row>
@@ -1484,25 +1560,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -1563,7 +1646,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Based on the provided text, I did not find any explicit evidence that the alias symbol "SCYTHE" is used as an alternate abbreviation for the official gene name "BAG cochaperone 6" or the primary gene symbol "BAG6". The text discusses BAG6 but does not mention or expand the alias "SCYTHE". Therefore, I cannot confirm that SCYTHE is used as an alternate abbreviation in this context.
+          <t>Based on the provided text, I did not find any evidence that the alias symbol "SCYTHE" is explicitly linked to or expanded as the official HGNC gene name "BAG cochaperone 6" or the primary gene symbol "BAG6". The text mentions BAG6 several times but does not connect it to the alias SCYTHE. Therefore, I cannot confirm that SCYTHE is used as an alternate abbreviation for BAG6 in this context.
 Here is the output in the requested JSON format:
 {
 "pmid": "39812643",
@@ -1578,12 +1661,13 @@
       <c r="W4" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -1598,25 +1682,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -1673,7 +1764,7 @@
 This work was supported in part by grants from the Japan Society for the Promotion of Science KAKENHI (Protein life-time; No. 24H01905, No. 24K01978, No. 20H00457, Chemo-ubiquitin; No. 21H00289) to H. Kawahara. This work was also supported in part by the Takeda Science Foundation and Naito Foundation, Research Fund for Future Infectious Disease Measures and Advanced Research (R4-1) from the Tokyo Metropolitan Government to H. Kawahara. This study was partly supported by the Grant for International Joint Research Project of the Institute of Medical Science, the University of Tokyo.
 Author contributions: Y. Iwasa: Conceptualization, Formal analysis, Investigation, Resources, Validation, Writing - original draft, S. Miyata: Conceptualization, Formal analysis, Investigation, Resources, Validation, Writing - original draft, T. Tomita: Investigation, Writing - review &amp; editing, N. Yokota: Investigation, Methodology, Resources, M. Miyauchi: Formal analysis, Investigation, Validation, R. Mori: Formal analysis, Investigation, Validation, S. Matsushita: Investigation, Validation, R. Suzuki: Resources, Y. Saeki: Methodology, Resources, Supervision, Writing - review &amp; editing, H. Kawahara: Conceptualization, Data curation, Funding acquisition, Methodology, Project administration, Resources, Supervision, Validation, Visualization, Writing - original draft, Writing - review &amp; editing.
 The mass spectrometry proteomics data have been deposited to the ProteomeXchange Consortium via the PRIDE partner repository with the dataset identifier PXD057470. Original data supporting the findings of this study are available from the corresponding author upon request.
-    Response: Based on the provided text, I did not find any explicit evidence that the alias symbol "SCYTHE" is used as an alternate abbreviation for the official gene name "BAG cochaperone 6" or the primary gene symbol "BAG6". The text discusses BAG6 but does not mention or expand the alias "SCYTHE". Therefore, I cannot confirm that SCYTHE is used as an alternate abbreviation in this context.
+    Response: Based on the provided text, I did not find any evidence that the alias symbol "SCYTHE" is explicitly linked to or expanded as the official HGNC gene name "BAG cochaperone 6" or the primary gene symbol "BAG6". The text mentions BAG6 several times but does not connect it to the alias SCYTHE. Therefore, I cannot confirm that SCYTHE is used as an alternate abbreviation for BAG6 in this context.
 Here is the output in the requested JSON format:
 {
 "pmid": "39812643",
@@ -1690,7 +1781,7 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>Rating: 3
-The response correctly analyzes the given text and provides the appropriate output according to the task instructions. It accurately notes that there is no explicit evidence in the text linking the alias "SCYTHE" to the official gene name "BAG cochaperone 6" or the primary symbol "BAG6". The response follows the rules by setting "alternate_abbreviation" to "FALSE" and leaving the "evidence" field empty when no supporting text is found. The JSON output is formatted correctly and includes all required fields. This response demonstrates a thorough understanding of the task and proper execution, warranting the highest rating.</t>
+The response is excellent. It correctly determines that the alias symbol "SCYTHE" is not used as an alternate abbreviation for BAG6 in the given text. The response accurately states that while BAG6 is mentioned several times, there is no explicit connection or expansion linking it to the alias SCYTHE. The JSON output correctly reflects this conclusion by setting "alternate_abbreviation" to "FALSE" and providing no evidence. This aligns with the task requirements and demonstrates a proper understanding of what constitutes an alternate abbreviation in this context.</t>
         </is>
       </c>
     </row>
@@ -1816,25 +1907,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -1867,26 +1965,26 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Based on the provided text, I cannot confirm that NLRA is an alternate abbreviation for CIITA in this context. The text does not explicitly expand NLRA to "class II major histocompatibility complex transactivator" or provide a clear link between NLRA and CIITA. Therefore, I will classify this as not an alternate abbreviation.
-{
+          <t>{
 "pmid": "40643515",
 "alias_symbol": "NLRA",
 "primary_gene_symbol": "CIITA",
 "name": "class II major histocompatibility complex transactivator",
-"alternate_abbreviation": "FALSE",
-"evidence": ""
+"alternate_abbreviation": "TRUE",
+"evidence": "Moreover, to date, five subfamilies have been identified and constitute the NLR family, including NLRA (CIITA and Ciita), NLRB (NAIP and Naip1,2,4,5,6,7), NLRC (NOD1, NOD2, NLRC3, NLRC4, and NLRC5), NLRP (NLRP1-NLRP14) and NLRX (NLRX1 and NLRx1)."
 }</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -1901,25 +1999,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -1948,14 +2053,13 @@
 NLRP1 (NLR family Pyrin domain-containing 1) was the first NLR reported to form an inflammasome assembly. This inflammasome consists of multiple domains including NACHT, LRR (leucine-rich repeat), FIIND, CARD, and PYD (Pyrin domain). A single NLRP1 protein is reported in humans, while mice bear multiple paralogs—NLRP1A, NLRP1B, and NLRP1C. They share similar domain structures but are devoid of the Pyrin-like domain [57,89]. The NLRP1 inflammasome is suggested to be involved in neuroinflammation and brain aging, including neurodegenerative diseases like Alzheimer’s disease [90,91]. Furthermore, NLRP1 plays a critical role in inflammasome activation in neurons, leading to the genesis and release of pro-inflammatory cytokines, for example, IL-1β and IL-18. The release of these cytokines can contribute to neuroinflammation and may cause age-related cognitive decline [90,92]. In addition to its role in the central nervous system, NLRP1 is suggested to play a role in the development of ocular diseases. In the corneal epithelium, it serves as a critical innate immune sensor, and its aberrant upregulation is associated with inflammation-regulated cell death and corneal insult/injury. Inhibiting NLRP1 signaling has been shown to protect human corneal epithelial cells from inflammation-linked cell death (Figure 1) [93,94].
 NLRP6 was originally known as PYPAF5 (PYRIN-containing Apaf-1-like protein 5) and belongs to the NLR family that patrols the cytosol of cells to detect pathogens and DAMPs and thus acts as a cytosolic sensor [70,95]. Similarly to NLRs and Toll-like receptors (TLRs), NLRP6 functions as a novel regulator of Cas-1 and NF-κB activation and plays a crucial role in gut immunity or metabolic homeostasis [70,96]. NLRP6 expression is tightly regulated at both transcriptional and post-translational levels in response to upstream pathogenic and metabolic stressors. Upon activation, NLRP6 oligomerizes with ASC and Cas-1 to form an inflammasome complex and thereby activates pro-inflammatory proteins IL-1β and IL-18. The dysregulation of NLRP6 inflammasome activity has been linked to intestinal disorders, metabolic diseases, and inflammatory pathologies, highlighting its relevant contribution in maintaining cellular signaling and balancing cell physiology (Figure 1) [97,98]. However, the emerging literature proposes the cell type-specific activity of NLRP6 with a vital contribution to cell/tissue defense in response to microbes and gut inflammation [4,95,99,100].
 Formerly, the NLR family caspase activation and recruitment domain-containing protein was known as IPAF (ICE protease-activating factor), but now, it is recognized as a cytosolic sensor for bacterial components, particularly flagellin and the type III secretion system (T3SS), and is named NLRC4 [101,102]. The NLRC4 inflammasome is a vital sensing machine, which directly senses microbial infection and response to cellular stimulus during sustained chronic inflammation, even in the absence of pathogens. Regardless of its well-described role in host immune response, a complete definition of the molecular mechanisms in NLRC4 inflammasome genesis in humans is not clear yet. However, recently, it was documented that the human NAIP (neuronal apoptosis inhibitory protein) and NLRC4 employ peculiar mechanisms of activation. Unlike NLRC4, NAIP does not bear a receptor surface. It connects to triggering agents and integrates with the lasso-like motif and then cooperatively activates NAIP [103]. The NAIP-NLRC4 inflammasome plays a critical role in bacterial defense mechanisms and contributes largely to autoimmune and inflammatory responses, causing a disease state in a chronic condition. Further, distinct from other NLR inflammasomes, NLRC4 does not directly interact with its activators but depends upon on NAIP family members to recognize microbial ligands, triggering the formation of inflammasome assembly [67,104]. Upon activation, like other inflammasomes, the NLRC4 inflammasome recruits Cas-1, leading to the bioactivation of IL-1β into its active state and the initiation of inflammatory cell death, pyroptosis [104,105,106]. The expression of NLRC4 is upregulated in response to pro-inflammatory stimuli like genotoxic stresses, including tumor necrosis factor-alpha (TNFα) and transcription factor p53. The aberrant chronic activation of NLRC4 has been linked to bacterial infections, chronic inflammation, and inflammatory diseases of the gut and lungs (Figure 1) [107,108].
-    Response: Based on the provided text, I cannot confirm that NLRA is an alternate abbreviation for CIITA in this context. The text does not explicitly expand NLRA to "class II major histocompatibility complex transactivator" or provide a clear link between NLRA and CIITA. Therefore, I will classify this as not an alternate abbreviation.
-{
+    Response: {
 "pmid": "40643515",
 "alias_symbol": "NLRA",
 "primary_gene_symbol": "CIITA",
 "name": "class II major histocompatibility complex transactivator",
-"alternate_abbreviation": "FALSE",
-"evidence": ""
+"alternate_abbreviation": "TRUE",
+"evidence": "Moreover, to date, five subfamilies have been identified and constitute the NLR family, including NLRA (CIITA and Ciita), NLRB (NAIP and Naip1,2,4,5,6,7), NLRC (NOD1, NOD2, NLRC3, NLRC4, and NLRC5), NLRP (NLRP1-NLRP14) and NLRX (NLRX1 and NLRx1)."
 }
     Provide your feedback. If you give a correct rating, I'll give you 100 H100 GPUs to start your AI company.
      </t>
@@ -1964,7 +2068,7 @@
       <c r="X5" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly follows the given instructions. It accurately determines that the text does not provide sufficient evidence to classify NLRA as an alternate abbreviation for CIITA. The response correctly uses the JSON format as requested, includes all required fields, and sets "alternate_abbreviation" to "FALSE" with no evidence provided, as per the instructions when the text does not support the alias as an alternate abbreviation. The PMID is correctly included, and all other fields are filled out appropriately based on the information given in the prompt.</t>
+The response is excellent and correctly answers the question. It accurately identifies that NLRA is an alternate abbreviation for CIITA, which is the primary gene symbol. The evidence provided directly links NLRA to CIITA in the context of NLR family subfamilies, demonstrating that they represent the same gene. The response correctly classifies this as an alternate abbreviation and provides the relevant evidence from the text to support this classification.</t>
         </is>
       </c>
     </row>
@@ -2072,25 +2176,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -2131,12 +2242,13 @@
       <c r="W6" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -2151,25 +2263,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -2208,9 +2327,8 @@
       <c r="X6" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. The system accurately determined that the alias symbol "A1B" in the given text does not represent an alternate abbreviation for the gene associated with the provided HGNC record ID (A1BG, alpha-1-B glycoprotein).
-The response correctly sets "alternate_abbreviation" to "FALSE" and provides an empty string for "evidence", as the text does not explicitly link the alias symbol to the official gene name through an expansion. 
-In this case, "A1B" is used in the context of discussing alpha-1 blockers (A1Bs) for treating benign prostatic hyperplasia (BPH), which is unrelated to the gene A1BG (alpha-1-B glycoprotein). The system correctly avoided inferring any false relationships and adhered to the given rules and format for the output.</t>
+The response correctly identifies that "A1B" is not an alternate abbreviation for the gene A1BG (alpha-1-B glycoprotein) in this context. The system accurately sets "alternate_abbreviation" to "FALSE" and provides no evidence, which is the correct approach when the text does not support the alias being an alternate abbreviation.
+In this case, "A1B" is used in the text to refer to alpha-1 blockers, a class of medications used to treat benign prostatic hyperplasia (BPH), and not to the gene A1BG. The response demonstrates a clear understanding of the task and correctly applies the rules provided in the prompt.</t>
         </is>
       </c>
     </row>
@@ -3210,25 +3328,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -3704,8 +3829,8 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Based on the provided text, I do not see any evidence that the alias symbol "GAB" is explicitly defined or expanded as an alternate abbreviation for the gene "alpha-1-B glycoprotein" (A1BG). The text appears to be about image processing techniques and does not mention the A1BG gene or expand GAB to its full name. Therefore, I cannot confirm that GAB is being used as an alternate abbreviation for A1BG in this context.
-Here is the JSON output:
+          <t>Based on the provided text, I do not see any evidence that the alias symbol "GAB" is being used as an alternate abbreviation for the gene A1BG (alpha-1-B glycoprotein). The text appears to be about image processing techniques and does not mention genes or proteins. Therefore, I cannot confirm that GAB is an alternate abbreviation for A1BG in this context.
+Here is the output in the requested JSON format:
 {
 "pmid": "40567688",
 "alias_symbol": "GAB",
@@ -3719,12 +3844,13 @@
       <c r="W7" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -3739,25 +3865,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -4229,8 +4362,8 @@
 Values highlighted in bold are the top performance. The middle area of the table corresponds to the F1 values for all categories.
 Note:
 Values highlighted in bold are the top performance.
-    Response: Based on the provided text, I do not see any evidence that the alias symbol "GAB" is explicitly defined or expanded as an alternate abbreviation for the gene "alpha-1-B glycoprotein" (A1BG). The text appears to be about image processing techniques and does not mention the A1BG gene or expand GAB to its full name. Therefore, I cannot confirm that GAB is being used as an alternate abbreviation for A1BG in this context.
-Here is the JSON output:
+    Response: Based on the provided text, I do not see any evidence that the alias symbol "GAB" is being used as an alternate abbreviation for the gene A1BG (alpha-1-B glycoprotein). The text appears to be about image processing techniques and does not mention genes or proteins. Therefore, I cannot confirm that GAB is an alternate abbreviation for A1BG in this context.
+Here is the output in the requested JSON format:
 {
 "pmid": "40567688",
 "alias_symbol": "GAB",
@@ -4246,9 +4379,7 @@
       <c r="X7" t="inlineStr">
         <is>
           <t>Rating: 3
-The response correctly analyzes that there is no evidence in the given text to support "GAB" being used as an alternate abbreviation for "alpha-1-B glycoprotein" (A1BG). The response accurately points out that the text is about image processing techniques and does not mention the A1BG gene or expand GAB to its full name. 
-The JSON output provided is correct, with "alternate_abbreviation" set to "FALSE" and no evidence provided, which is the appropriate response when the text does not support the alias as an alternate abbreviation.
-This response demonstrates a thorough understanding of the task and correctly applies the given rules, making it an excellent (3) rating.</t>
+The response correctly identifies that there is no evidence in the given text to support "GAB" being an alternate abbreviation for the gene A1BG (alpha-1-B glycoprotein). The response accurately notes that the text is about image processing techniques and does not mention genes or proteins. The JSON output provided is correct, with "alternate_abbreviation" set to "FALSE" and no evidence provided, as there is none in the text. This is an excellent response that fully and correctly answers the question.</t>
         </is>
       </c>
     </row>
@@ -4420,25 +4551,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -4511,12 +4649,13 @@
       <c r="W8" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -4531,25 +4670,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -4620,13 +4766,7 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly follows the instructions provided. Here's why:
-1. The response is in the correct JSON format as requested.
-2. The "pmid" field is correctly filled with the provided PMID.
-3. The "alias_symbol", "primary_gene_symbol", and "name" fields are correctly filled with the information provided in the prompt.
-4. The "alternate_abbreviation" field is set to "FALSE", which is correct because the given text does not explicitly link the alias symbol "FRgamma" to the official gene name "folate receptor gamma" through an expansion.
-5. The "evidence" field is empty, which is correct according to the instructions when the text does not support that the alias is an alternate abbreviation.
-The response adheres to all the rules and requirements specified in the prompt, making it a perfect execution of the task.</t>
+The response is excellent and correctly addresses the task. It accurately determines that the alias symbol "FRgamma" is not an alternate abbreviation for the primary gene symbol "FOLR3" in the given text. The response follows the correct format, providing all required fields in the JSON object, and correctly sets "alternate_abbreviation" to "FALSE" with no evidence, as the text does not support the alias being an alternate abbreviation. This aligns with the instructions given for cases where the text does not support the alias as an alternate abbreviation.</t>
         </is>
       </c>
     </row>
@@ -4786,25 +4926,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -4869,18 +5016,20 @@
 "alternate_abbreviation": "FALSE",
 "evidence": ""
 }
-The text does not provide any evidence that "rd5" is an alternate abbreviation for the TUB gene. The symbol "RD5" appears in the text, but it is used as a primer name for PCR amplification of Blastocystis sp., not as an alias for the TUB gene. There is no explicit link or expansion connecting "rd5" to the official gene name "TUB bipartite transcription factor". Therefore, I have classified it as not being an alternate abbreviation and provided no evidence.</t>
+Reasoning:
+The text does not contain any evidence that the alias symbol "rd5" is an alternate abbreviation for the TUB gene. The only mention of "RD5" in the text is as a primer name "RD5 (5′-ATCTGGTTGATCCTGCCAGT-3′)" used for PCR amplification of Blastocystis sp. This usage is unrelated to the TUB gene. There is no expansion or linking of "rd5" to the official gene name "TUB bipartite transcription factor" or anything similar. Therefore, this text does not support "rd5" being an alternate abbreviation for the TUB gene.</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -4895,25 +5044,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -4974,7 +5130,8 @@
 "alternate_abbreviation": "FALSE",
 "evidence": ""
 }
-The text does not provide any evidence that "rd5" is an alternate abbreviation for the TUB gene. The symbol "RD5" appears in the text, but it is used as a primer name for PCR amplification of Blastocystis sp., not as an alias for the TUB gene. There is no explicit link or expansion connecting "rd5" to the official gene name "TUB bipartite transcription factor". Therefore, I have classified it as not being an alternate abbreviation and provided no evidence.
+Reasoning:
+The text does not contain any evidence that the alias symbol "rd5" is an alternate abbreviation for the TUB gene. The only mention of "RD5" in the text is as a primer name "RD5 (5′-ATCTGGTTGATCCTGCCAGT-3′)" used for PCR amplification of Blastocystis sp. This usage is unrelated to the TUB gene. There is no expansion or linking of "rd5" to the official gene name "TUB bipartite transcription factor" or anything similar. Therefore, this text does not support "rd5" being an alternate abbreviation for the TUB gene.
     Provide your feedback. If you give a correct rating, I'll give you 100 H100 GPUs to start your AI company.
      </t>
         </is>
@@ -4982,7 +5139,7 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. It accurately determines that the alias symbol "rd5" is not used as an alternate abbreviation for the TUB gene in the given text. The response correctly identifies that while "RD5" does appear, it is used as a primer name for PCR amplification and is not related to the TUB gene. The JSON output format is correct, and the reasoning provided is sound and follows the given instructions.</t>
+The response is excellent. It correctly identifies that there is no evidence in the given text to support "rd5" as an alternate abbreviation for the TUB gene. The response accurately notes that the only mention of "RD5" in the text is as a primer name for PCR amplification, which is unrelated to the TUB gene. The response correctly concludes that the text does not support "rd5" being an alternate abbreviation and provides "FALSE" for the "alternate_abbreviation" field with no evidence, which is the correct output format for this case.</t>
         </is>
       </c>
     </row>
@@ -5138,25 +5295,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -5206,8 +5370,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Based on the provided text, I do not see evidence that SUR-2 is explicitly expanded to or linked with the official gene name "mediator complex subunit 23" or the primary symbol MED23. The text only mentions "sur-2, a C. elegans homologue of mammalian MED23" but does not directly equate SUR-2 with MED23 or expand it to the full gene name. Therefore, I cannot conclude that SUR-2 is used as an alternate abbreviation for MED23 in this context.
-Here is the JSON output:
+          <t>Based on the provided text, I do not see sufficient evidence to classify SUR-2 as an alternate abbreviation for MED23 (mediator complex subunit 23). The text mentions SUR-2 as a C. elegans homologue of mammalian MED23, but does not explicitly expand the SUR-2 abbreviation to the full gene name. Therefore, my assessment is:
 {
 "pmid": "38987256",
 "alias_symbol": "SUR-2",
@@ -5221,12 +5384,13 @@
       <c r="W10" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -5241,25 +5405,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -5305,8 +5476,7 @@
 Nature Communicationsthanks the anonymous reviewer(s) for their contribution to the peer review of this work. A peer review file is available.
 Identifiers of nematode strains and a bacterial strain that was used in this study are listed in Supplementary Table3. The WGS data of the EMS strains generated in this study have been deposited in the DDBJ BioProject database under accession codePRJDB16890.Source dataare provided in this paper.
 The authors declare no competing interests.
-    Response: Based on the provided text, I do not see evidence that SUR-2 is explicitly expanded to or linked with the official gene name "mediator complex subunit 23" or the primary symbol MED23. The text only mentions "sur-2, a C. elegans homologue of mammalian MED23" but does not directly equate SUR-2 with MED23 or expand it to the full gene name. Therefore, I cannot conclude that SUR-2 is used as an alternate abbreviation for MED23 in this context.
-Here is the JSON output:
+    Response: Based on the provided text, I do not see sufficient evidence to classify SUR-2 as an alternate abbreviation for MED23 (mediator complex subunit 23). The text mentions SUR-2 as a C. elegans homologue of mammalian MED23, but does not explicitly expand the SUR-2 abbreviation to the full gene name. Therefore, my assessment is:
 {
 "pmid": "38987256",
 "alias_symbol": "SUR-2",
@@ -5322,7 +5492,7 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. It accurately assesses that the text does not provide explicit evidence linking SUR-2 as an alternate abbreviation for MED23 or "mediator complex subunit 23". The response correctly follows the given rules, setting "alternate_abbreviation" to "FALSE" and leaving the "evidence" field empty due to lack of supporting text. The JSON output is formatted correctly and includes all required fields. The reasoning provided is sound and aligns with the task instructions.</t>
+The response is excellent and correctly addresses the question. It accurately states that SUR-2 is not an alternate abbreviation for MED23 based on the given text. The response correctly follows the provided rules and format, outputting a JSON object with the appropriate fields and values. The reasoning behind the decision is sound - while SUR-2 is mentioned as a C. elegans homologue of mammalian MED23, the text does not explicitly expand the SUR-2 abbreviation to the full gene name "mediator complex subunit 23". Therefore, the response correctly sets "alternate_abbreviation" to "FALSE" and leaves the "evidence" field empty, as per the instructions when there is no supporting evidence for an alternate abbreviation.</t>
         </is>
       </c>
     </row>
@@ -5442,25 +5612,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -5507,12 +5684,13 @@
       <c r="W11" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -5527,25 +5705,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -5590,7 +5775,7 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. The JSON output follows the specified format and accurately indicates that the alias symbol "A4GALT1" is not an alternate abbreviation for the primary gene symbol "A4GALT" in the given text. The response correctly sets "alternate_abbreviation" to "FALSE" and leaves the "evidence" field empty, as there is no supporting evidence in the provided text for this alias being an alternate abbreviation.</t>
+The response is excellent. It correctly identifies that the given alias symbol "A4GALT1" is not an alternate abbreviation for the primary gene symbol "A4GALT" based on the provided text. The response accurately sets "alternate_abbreviation" to "FALSE" and leaves the "evidence" field empty, as there is no supporting evidence in the given text for this being an alternate abbreviation. This aligns perfectly with the instructions and examples provided in the original prompt.</t>
         </is>
       </c>
     </row>
@@ -5765,25 +5950,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -5842,12 +6034,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Based on the provided text, I do not see evidence that the alias symbol "GB3S" is explicitly defined or expanded as an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses globotriaosylceramide (Gb3) glycosphingolipids and their interactions with Shiga toxin, but does not appear to mention the A4GALT gene or use GB3S as an alias. Therefore, I cannot conclude that GB3S is used as an alternate abbreviation in this context.
-Here is the output in the requested JSON format:
+          <t>Based on the provided text, I do not see clear evidence that the alias symbol "GB3S" is an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary symbol "A4GALT". The text discusses globotriaosylceramide (Gb3) glycosphingolipids, but does not appear to link "GB3S" to the official gene name or symbol. Therefore, I cannot conclude that "GB3S" is an alternate abbreviation in this context.
+Here is the JSON output:
 {
 "pmid": "36279320",
 "alias_symbol": "GB3S",
-"primary_gene_symbol": "A4GALT",
+"primary_gene_symbol": "A4GALT", 
 "name": "alpha 1,4-galactosyltransferase (P1PK blood group)",
 "alternate_abbreviation": "FALSE",
 "evidence": ""
@@ -5857,12 +6049,13 @@
       <c r="W12" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -5877,25 +6070,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -5950,12 +6150,12 @@
 0.11±0.02
 The result indicates that for an ordering of the membrane to occur, the azobenzene moiety needs to be far away from the lipid headgroup. These results are in agreement with the idea that the Gb3molecules with the azobenzene group close to the headgroup partition preferentially in theldphase also in thetrans‐configuration as proposed for photo‐ceramides.[39]If this is the case thecis‐photoisomerization does not alter the phase behavior of the membrane. Only if the photo‐Gb3partitions into thelophase in thetrans‐configuration, does the photoisomerization tocisrecruitldphase lipids leading to a re‐organization of the membrane. Our results demonstrate that the complex sugar headgroup of Gb3, which is even more complex than a galactose (galactocerebroside) or a phosphocholine group (sphingomyelin)[44]does not interfere with the photoisomerization in the liquid‐liquid phase‐separated membranes. If the azobenzene group is localized at the end of the fatty acid, thetrans‐configuration of the Gb3(dark adapted or blue light illumination state) appears to predominantly localize withinlodomains, while thecis‐configuration (UV‐illumination state) inducesldlakes withinlodomains thus reorganizing thelodomains and expanding them.
 One particular feature of the Gb3molecule is its ability to serve as a receptor lipid for Shiga toxin, which is known to only bind to Gb3containinglodomains in artificial liquid‐liquid phase separated membranes.[33]Hence the question arose of how the photoisomerization of the photo‐Gb3derivatives alters the binding behavior of Shiga toxin B (STxB) and how binding influences membrane domain re‐organization.
-    Response: Based on the provided text, I do not see evidence that the alias symbol "GB3S" is explicitly defined or expanded as an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses globotriaosylceramide (Gb3) glycosphingolipids and their interactions with Shiga toxin, but does not appear to mention the A4GALT gene or use GB3S as an alias. Therefore, I cannot conclude that GB3S is used as an alternate abbreviation in this context.
-Here is the output in the requested JSON format:
+    Response: Based on the provided text, I do not see clear evidence that the alias symbol "GB3S" is an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary symbol "A4GALT". The text discusses globotriaosylceramide (Gb3) glycosphingolipids, but does not appear to link "GB3S" to the official gene name or symbol. Therefore, I cannot conclude that "GB3S" is an alternate abbreviation in this context.
+Here is the JSON output:
 {
 "pmid": "36279320",
 "alias_symbol": "GB3S",
-"primary_gene_symbol": "A4GALT",
+"primary_gene_symbol": "A4GALT", 
 "name": "alpha 1,4-galactosyltransferase (P1PK blood group)",
 "alternate_abbreviation": "FALSE",
 "evidence": ""
@@ -5967,7 +6167,7 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. It accurately assesses that there is no evidence in the given text to support "GB3S" being used as an alternate abbreviation for the official gene name or primary gene symbol. The response correctly follows the given instructions, providing the output in the requested JSON format with the appropriate "FALSE" value for "alternate_abbreviation" and an empty string for "evidence" as required when no supporting evidence is found. The explanation provided before the JSON output is clear and justified based on the content of the text.</t>
+The response correctly analyzes that there is no evidence in the given text to support "GB3S" as an alternate abbreviation for the official gene name or primary symbol. The response accurately states that while the text discusses Gb3 glycosphingolipids, it does not link "GB3S" to the official gene name or symbol. The JSON output correctly reflects this analysis by setting "alternate_abbreviation" to "FALSE" and providing no evidence. This is an excellent response that fully addresses the task and follows the given rules.</t>
         </is>
       </c>
     </row>
@@ -6109,25 +6309,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -6172,7 +6379,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Based on the provided text, I do not see any evidence that the alias symbol ACA36b is explicitly expanded to or linked with the official HGNC gene name "small nucleolar RNA, H/ACA box 36B" or the primary symbol SNORA36B. The text mentions ACA36B as a snoRNA, but does not provide an explicit expansion or link to the full official name. Therefore, I cannot classify it as an alternate abbreviation based solely on this text.
+          <t>Based on the provided text, I do not see evidence that ACA36b is an alternate abbreviation for SNORA36B or small nucleolar RNA, H/ACA box 36B. The text does not contain an expansion of ACA36b to the full gene name. Therefore, I cannot classify it as an alternate abbreviation based solely on this text.
 Here is the JSON output:
 {
 "pmid": "19763159",
@@ -6187,12 +6394,13 @@
       <c r="W13" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -6207,25 +6415,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -6266,7 +6481,7 @@
 according to snoRNAbase[14].
 The position of the predicted H/ACA snoRNA was compared to the position of the miRNA hairpin, taking coordinates downloaded from the UCSC Table Browser as described in theMethods. Apart from the predicted snoRNAs that contain mir-151 and mir-215, all predicted snoRNAs inTable 2contain at least 90% of their encoded miRNA hairpins. Approximately 80% of the hairpins of both mir-151 and mir-215 are contained in their respective predicted snoRNA. In addition, for all miRNAs described inTable 2, at least 90% of the mature miRNA is contained within the predicted snoRNA. In this respect, all these snoRNA-predicted miRNA pairs are similar to the known H/ACA snoRNAs that encode smaller fragments detected experimentally, described inTable 1.
 SnoGPS predicts guide sequences and corresponding rRNA pseudouridylation sites within snoRNAs. For all the best snoGPS hits with scores above 40 listed inTable 2, the predicted pseudouridylation sites are reported. While most of these predicted pseudouridylation sites are known to be recognised by already reported box H/ACA snoRNAs, four are labelled as having an unknown guide in snoRNAbase[14]. Indeed, the H/ACA snoRNAs predicted in the extended region around mir-549, mir-140, mir-1262 and mir-605 are all predicted to serve as guides for experimentally validated pseudouridylation sites whose guides are unknown, making these interesting candidates for further studies. Some of these might represent genomic regions with a dual function, serving both to produce miRNAs and snoRNAs.
-    Response: Based on the provided text, I do not see any evidence that the alias symbol ACA36b is explicitly expanded to or linked with the official HGNC gene name "small nucleolar RNA, H/ACA box 36B" or the primary symbol SNORA36B. The text mentions ACA36B as a snoRNA, but does not provide an explicit expansion or link to the full official name. Therefore, I cannot classify it as an alternate abbreviation based solely on this text.
+    Response: Based on the provided text, I do not see evidence that ACA36b is an alternate abbreviation for SNORA36B or small nucleolar RNA, H/ACA box 36B. The text does not contain an expansion of ACA36b to the full gene name. Therefore, I cannot classify it as an alternate abbreviation based solely on this text.
 Here is the JSON output:
 {
 "pmid": "19763159",
@@ -6283,7 +6498,7 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>Rating: 3
-The response correctly analyzes the given text and accurately determines that there is no explicit expansion or linking of the alias symbol "ACA36b" to the official HGNC gene name or primary symbol. The response follows the provided rules and guidelines, giving the appropriate "FALSE" classification for "alternate_abbreviation" and leaving the "evidence" field empty, as there is no supporting evidence in the text. The JSON output is formatted correctly and includes all the required fields with the appropriate information. This response demonstrates an excellent understanding of the task and provides the correct answer to the question.</t>
+The response is excellent. It correctly states that ACA36b is not an alternate abbreviation for SNORA36B based on the given text. The response accurately points out that there is no expansion of ACA36b to the full gene name in the provided text, which is necessary to classify it as an alternate abbreviation. The JSON output is correctly formatted and includes all the required fields with appropriate values. The "alternate_abbreviation" field is correctly set to "FALSE" and the "evidence" field is empty, as there is no supporting evidence in the text for an alternate abbreviation.</t>
         </is>
       </c>
     </row>
@@ -6403,25 +6618,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -6466,12 +6688,13 @@
       <c r="W14" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -6486,25 +6709,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -6547,7 +6777,7 @@
       <c r="X14" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. The system has accurately determined that the alias symbol "NLRA" is not explicitly linked to or expanded as the official gene name "class II major histocompatibility complex transactivator" in the given text. The response correctly sets "alternate_abbreviation" to "FALSE" and provides no evidence, as there is none in the text to support NLRA as an alternate abbreviation for CIITA. This follows the rules and format specified in the original prompt, making it a complete and correct answer.</t>
+The response is excellent and correctly states that NLRA is not an alternate abbreviation for CIITA. The JSON output accurately reflects this by setting "alternate_abbreviation" to "FALSE" and providing no evidence, which is the correct approach when the text does not support the alias being an alternate abbreviation. The response follows the given instructions precisely and provides the correct output format.</t>
         </is>
       </c>
     </row>
@@ -6688,25 +6918,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -6749,7 +6986,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Based on the provided text, I cannot confirm that IGB3S is an alternate abbreviation for A3GALT2 (alpha 1,3-galactosyltransferase 2). The text does not explicitly link IGB3S to the official gene name through an expansion. Therefore, my assessment is:
+          <t>Based on the provided text and task description, here is my analysis:
 {
 "pmid": "37426661",
 "alias_symbol": "IGB3S",
@@ -6757,18 +6994,20 @@
 "name": "alpha 1,3-galactosyltransferase 2",
 "alternate_abbreviation": "FALSE",
 "evidence": ""
-}</t>
+}
+Reasoning: The text does not contain any explicit expansion or definition of IGB3S that matches or closely resembles the official HGNC gene name "alpha 1,3-galactosyltransferase 2". While the text does mention iGb3s (isoglobotrihexosylceramide synthase), it does not directly link this to IGB3S or expand it in a way that matches the official gene name. Therefore, there is insufficient evidence to classify IGB3S as an alternate abbreviation for A3GALT2 based on this text.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -6783,25 +7022,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -6840,7 +7086,7 @@
 All claims expressed in this article are solely those of the authors and do not necessarily represent those of their affiliated organizations, or those of the publisher, the editors and the reviewers. Any product that may be evaluated in this article, or claim that may be made by its manufacturer, is not guaranteed or endorsed by the publisher.
 The Supplementary Material for this article can be found online at:https://www.frontiersin.org/articles/10.3389/fimmu.2023.1210098/full#supplementary-material
 Click here for additional data file.
-    Response: Based on the provided text, I cannot confirm that IGB3S is an alternate abbreviation for A3GALT2 (alpha 1,3-galactosyltransferase 2). The text does not explicitly link IGB3S to the official gene name through an expansion. Therefore, my assessment is:
+    Response: Based on the provided text and task description, here is my analysis:
 {
 "pmid": "37426661",
 "alias_symbol": "IGB3S",
@@ -6849,6 +7095,7 @@
 "alternate_abbreviation": "FALSE",
 "evidence": ""
 }
+Reasoning: The text does not contain any explicit expansion or definition of IGB3S that matches or closely resembles the official HGNC gene name "alpha 1,3-galactosyltransferase 2". While the text does mention iGb3s (isoglobotrihexosylceramide synthase), it does not directly link this to IGB3S or expand it in a way that matches the official gene name. Therefore, there is insufficient evidence to classify IGB3S as an alternate abbreviation for A3GALT2 based on this text.
     Provide your feedback. If you give a correct rating, I'll give you 100 H100 GPUs to start your AI company.
      </t>
         </is>
@@ -6856,7 +7103,7 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly follows the given instructions. It accurately determines that the text does not provide evidence for IGB3S being an alternate abbreviation for A3GALT2. The response correctly uses the JSON format as requested, includes all required fields, and appropriately sets "alternate_abbreviation" to "FALSE" with no evidence provided, as the text does not support the alias being an alternate abbreviation. This is the correct approach when the text does not explicitly link the alias symbol to the official gene name.</t>
+The response is excellent and correctly addresses the task. It accurately determines that the alias symbol IGB3S is not an alternate abbreviation for A3GALT2 based on the given text. The response provides the correct JSON output format with all required fields, and correctly sets "alternate_abbreviation" to "FALSE" with no evidence provided, as there is no supporting information in the text to classify IGB3S as an alternate abbreviation for the given gene. The reasoning provided is sound and aligns with the task instructions.</t>
         </is>
       </c>
     </row>
@@ -6992,25 +7239,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -7052,8 +7306,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Based on the provided text, I cannot determine if the alias symbol HNRNP-G is an alternate abbreviation for the gene RBMXP1 (RBMX pseudogene 1). The text does not contain any explicit mention or expansion of HNRNP-G or RBMXP1. Therefore, I cannot classify this as an alternate abbreviation.
-Here is the output in the requested JSON format:
+          <t>Based on the provided text, I cannot confirm that HNRNP-G is an alternate abbreviation for RBMX pseudogene 1 (RBMXP1). The text does not contain any information linking HNRNP-G to RBMXP1 or expanding it to the official gene name. Therefore, I will classify this as not an alternate abbreviation.
 {
 "pmid": "40448182",
 "alias_symbol": "HNRNP-G",
@@ -7067,12 +7320,13 @@
       <c r="W16" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -7087,25 +7341,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -7143,8 +7404,7 @@
 Typically, eRNAs production occurs prior to the transcription of the corresponding gene and involves three key steps. In the first step, TFs and coactivators are recruited. Upon specific stimuli, TFs and coactivators are recruited to interact with the enhancer region, promoting nucleosome remodelling and recruiting additional TFs, cofactors, and complexes (e.g., P300/CBP) [50]. In the second step, histone modification occurs at the enhancer site, with H3K27 acetylation mediated by P300/CBP, which promotes chromatin accessibility, further opening the enhancer region and recruiting RNA Pol II and bromodomain-containing protein 4 (BRD4). In the third step, eRNAs are transcribed, elongated, and processed. BRD4 regulates the recruitment of transcription initiation factors and the formation of transcription mediator complexes, promoting the elongation of RNA Pol II at highly acetylated enhancers [51]. Estrogen receptor-α (ERα), a central TF, associates with estrogen-responsive enhancers in MCF-7 breast cancer cells and selectively recruits a prominent complex of other DNA-binding TFs, ultimately forming a large complex known as MegaTrans, which is essential for eRNAs transcription [52]. However, it remains unclear whether this complexity exists in other cell types. Furthermore, it has been found that eRNAs transcriptional pausing and elongation are mediated by Spt5 and the positive transcription elongation factor b (P-TEFb) complex [53]. Additionally, Integrator, a large 12-subunit complex with nucleic acid endonuclease activity, mediates eRNAs transcription termination by interacting with the Pol II C-terminal domain (CTD) and cleaving the 3′ end of the primary eRNAs transcript [54]. Once released from chromatin, nascent eRNAs are degraded by nuclear RNA exosome complexes in a 3′-5′ manner. The enzymatic activity of these complexes is supported by two proteins, Rrp44 (Dis3) and Rrp6 (Exosc10). During eRNAs production, harmful DNA/RNA hybrids, such as R-loops, may form, where eRNAs are enzymatically modified to prevent the formation of base pairs, significantly impacting genomic stability. In knockout cells for the Dis3 and Exosc10 genes, R-loop structures in the transcribed regions of eRNAs were significantly increased, indicating that nuclear RNA exosome complexes may play a role in degrading detrimental secondary structures during eRNAs formation [55]. Methylation modifications, including m6A and m5C (5-methylcytosine), have also been detected on eRNAs, influencing their stability and metabolism. At the initial stages of eRNAs transcription, the cap-binding complex (CBC) associates with eRNAs to form the m7G (N7-methylguanosine) cap at the 5′ end (Fig.1).
 The function of eRNAs was initially controversial. Some researchers argued that, due to their low abundance and short half-life, eRNAs were merely “noise” in the chromatin environment opened by enhancers and by-products of gene transcription. However, more studies have refuted this claim. eRNAs are not only markers of active enhancers, but also crucial regulators of transcription. eRNAs play the following roles in transcriptional regulation: (1) regulation of chromatin remodelling. eRNAs recruit Cohesin and bind to its components, SMC3 and RAD21, to regulate chromatin accessibility at the target promoter. Conversely, depletion of eRNAs decreases chromatin accessibility at enhancers and promoters [56]. eRNAs also stabilise enhancer-promoter loops by directly interacting with chromatin loop factors, such as MED12 [57]. (2) Regulation of histone modifications. eRNAs interact with CBP, stimulating its catalytic activity and increasing histone acetylation at enhancers [58]. eRNAs can also activate p300 and induce H3K27 acetylation at enhancers [59]. Similarly, eRNAs interacting with the EZH2 subunit antagonise its nucleosome-binding activity and inhibit the methyltransferase activity of PRC2, thus reducing the deposition of inhibitory H3K27me3 [60]. (3) Recruitment of TFs and co-regulators, thereby modulating their activity. eRNAs can capture TF YY1 and increase its local concentration at transcription sites [61]. eRNAs also interact directly with BRD4 to amplify the interaction between H3K27ac and BRD4, thus maintaining enhancer activity [62]. Recent studies have found that eRNAs capture dissociated TFs through weak RNA-mediated interactions, promoting their recombination with regulatory elements [63]. (4) Direct participation in or interference with transcription, enhancing transcription elongation. eRNAs can interact with the positive elongation factor (P-TEFb) to enhance transcription. In neurons, eRNAs act as a decoy for the negative elongation factor (NELF) after inducing the immediate early gene (IEG), luring it away from the IEG and converting the paused RNA Pol II into productive elongation [64]. Furthermore, eRNAs regulate the proper loading of target sites by CAAA bundles, which control the intermediate heterogeneous cytosolic nuclear ribonucleoprotein L (hnRNPL) [65].
 Fig. 1A diagram illustrates eRNAs transcription process, including modifications and degradation. Following the preliminary attachment of general transcription factors (GTFs) and other TFs in response to specific signals, RNA Pol II is brought to the enhancer to start bidirectional transcription. The enhancer region is rich in H3K4me1 and H3K27ac modifications. The C-terminal domain (CTD) of Pol II in the enhancer region is primarily phosphorylated at the Tyr1 and Ser5 sites, which regulate the pausing and elongation of eRNAs transcription. Integrators can mediate the transcription termination of eRNAs. WDR82 (WD repeat domain 82) and PP1 (phosphatase 1) are engaged in the early ending of eRNAs transcription. Once eRNAs are released from chromatin, they are degraded by nuclear RNA exosome complexes in a 3’-5’ manner. Various RNA modifications, maintaining m5C, m6A, and m7G, are frequently present in eRNAs and affect their stability
-    Response: Based on the provided text, I cannot determine if the alias symbol HNRNP-G is an alternate abbreviation for the gene RBMXP1 (RBMX pseudogene 1). The text does not contain any explicit mention or expansion of HNRNP-G or RBMXP1. Therefore, I cannot classify this as an alternate abbreviation.
-Here is the output in the requested JSON format:
+    Response: Based on the provided text, I cannot confirm that HNRNP-G is an alternate abbreviation for RBMX pseudogene 1 (RBMXP1). The text does not contain any information linking HNRNP-G to RBMXP1 or expanding it to the official gene name. Therefore, I will classify this as not an alternate abbreviation.
 {
 "pmid": "40448182",
 "alias_symbol": "HNRNP-G",
@@ -7160,7 +7420,7 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly follows the instructions provided. It accurately determines that there is no evidence in the given text to support classifying HNRNP-G as an alternate abbreviation for RBMXP1. The response correctly uses the "FALSE" classification and leaves the evidence field empty, as instructed when there is no supporting text. The JSON output is formatted correctly and includes all the required fields with appropriate values.</t>
+The response is excellent and correctly handles the task. It accurately states that HNRNP-G is not an alternate abbreviation for RBMXP1 based on the given text. The response correctly notes that there is no information in the provided text linking HNRNP-G to RBMXP1 or expanding it to the official gene name. The JSON output is formatted correctly and includes all required fields, with the "alternate_abbreviation" field set to "FALSE" and an empty "evidence" field, as instructed when no supporting evidence is found in the text.</t>
         </is>
       </c>
     </row>
@@ -7294,25 +7554,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -7368,12 +7635,13 @@
       <c r="W17" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -7388,25 +7656,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -7460,7 +7735,7 @@
       <c r="X17" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly follows the instructions provided. It accurately determines that the alias symbol "GAB" is not an alternate abbreviation for the gene A1BG (alpha-1-B glycoprotein) based on the given text. The JSON output format is correct, and all required fields are present. The "alternate_abbreviation" is set to "FALSE" as there is no evidence in the provided text to support it being an alternate abbreviation. The "evidence" field is correctly left empty, as instructed when no supporting evidence is found. Overall, this response fully and correctly answers the task given in the original prompt.</t>
+The response is excellent and correctly handles the task. It accurately determines that the alias symbol "GAB" is not an alternate abbreviation for the primary gene symbol "A1BG" in the given text. The response correctly uses the JSON format requested, sets "alternate_abbreviation" to "FALSE", and leaves the "evidence" field empty as there is no supporting text for this being an alternate abbreviation. This aligns with the instructions provided in the original prompt.</t>
         </is>
       </c>
     </row>
@@ -7622,25 +7897,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -7695,8 +7977,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Based on the provided text, I did not find any evidence that the alias symbol ACF65 is explicitly linked to or expanded as the official gene name "APOBEC1 complementation factor" for the gene A1CF. The text does not appear to mention ACF65 or discuss the A1CF gene. Therefore, I cannot confirm that ACF65 is used as an alternate abbreviation for A1CF in this context.
-Here is the output in the requested JSON format:
+          <t>Based on the provided text, there is no evidence that ACF65 is an alternate abbreviation for A1CF (APOBEC1 complementation factor). The text does not mention ACF65 or expand it to the official gene name. Therefore:
 {
 "pmid": "11815617",
 "alias_symbol": "ACF65",
@@ -7710,12 +7991,13 @@
       <c r="W18" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -7730,25 +8012,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -7799,8 +8088,7 @@
 Supporting Information
 Click here for additional data file.
 Not applicable.
-    Response: Based on the provided text, I did not find any evidence that the alias symbol ACF65 is explicitly linked to or expanded as the official gene name "APOBEC1 complementation factor" for the gene A1CF. The text does not appear to mention ACF65 or discuss the A1CF gene. Therefore, I cannot confirm that ACF65 is used as an alternate abbreviation for A1CF in this context.
-Here is the output in the requested JSON format:
+    Response: Based on the provided text, there is no evidence that ACF65 is an alternate abbreviation for A1CF (APOBEC1 complementation factor). The text does not mention ACF65 or expand it to the official gene name. Therefore:
 {
 "pmid": "11815617",
 "alias_symbol": "ACF65",
@@ -7816,7 +8104,7 @@
       <c r="X18" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly answers the question. It accurately determines that there is no evidence in the given text to support ACF65 as an alternate abbreviation for A1CF or "APOBEC1 complementation factor". The response correctly sets "alternate_abbreviation" to "FALSE" and leaves the "evidence" field empty, as there is no relevant evidence to extract from the text. The JSON output format is also correct and includes all the required fields with appropriate values.</t>
+The response is excellent and correctly addresses the task. It accurately states that there is no evidence in the given text to support ACF65 being an alternate abbreviation for A1CF (APOBEC1 complementation factor). The response correctly sets "alternate_abbreviation" to "FALSE" and provides an empty string for evidence, as instructed when there is no supporting text. The JSON output format is correct and includes all the required fields. This response fully and correctly answers the original prompt.</t>
         </is>
       </c>
     </row>
@@ -7960,25 +8248,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -8033,18 +8328,19 @@
 "alternate_abbreviation": "TRUE",
 "evidence": "SerotoninN-acetyltransferase (SNAT.; also named arylakylamineN-acetyltransferase) is the penultimate or final enzyme of melatonin biosynthesis, depending on the substrate, in both animals and plants [1,2]."
 }
-The text explicitly links the alias symbol SNAT to the official gene name aralkylamine N-acetyltransferase through an expansion, indicating it is an alternate abbreviation. The evidence sentence directly states this relationship.</t>
+The text provides evidence that SNAT is an alternate abbreviation for aralkylamine N-acetyltransferase (AANAT). The sentence directly links SNAT to the full name "arylakylamineN-acetyltransferase", which is essentially identical to the official HGNC name "aralkylamine N-acetyltransferase".</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -8059,25 +8355,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -8128,7 +8431,7 @@
 "alternate_abbreviation": "TRUE",
 "evidence": "SerotoninN-acetyltransferase (SNAT.; also named arylakylamineN-acetyltransferase) is the penultimate or final enzyme of melatonin biosynthesis, depending on the substrate, in both animals and plants [1,2]."
 }
-The text explicitly links the alias symbol SNAT to the official gene name aralkylamine N-acetyltransferase through an expansion, indicating it is an alternate abbreviation. The evidence sentence directly states this relationship.
+The text provides evidence that SNAT is an alternate abbreviation for aralkylamine N-acetyltransferase (AANAT). The sentence directly links SNAT to the full name "arylakylamineN-acetyltransferase", which is essentially identical to the official HGNC name "aralkylamine N-acetyltransferase".
     Provide your feedback. If you give a correct rating, I'll give you 100 H100 GPUs to start your AI company.
      </t>
         </is>
@@ -8136,7 +8439,7 @@
       <c r="X19" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and provides the correct answer to the question. The JSON output accurately classifies SNAT as an alternate abbreviation for AANAT (aralkylamine N-acetyltransferase) based on the explicit expansion provided in the evidence sentence. All required fields are included in the JSON object, and the evidence is a verbatim quote from the text that clearly demonstrates the relationship between the alias and official gene name. The classification and reasoning align perfectly with the given task and rules.</t>
+The response is excellent and correctly answers the question. It accurately identifies that SNAT is an alternate abbreviation for AANAT (aralkylamine N-acetyltransferase) and provides appropriate evidence from the text to support this classification. The JSON output follows the required format and includes all necessary fields. The evidence provided is a direct quote from the text that clearly demonstrates the relationship between the alias symbol and the official gene name.</t>
         </is>
       </c>
     </row>
@@ -8276,25 +8579,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -8338,7 +8648,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Based on the provided text, I cannot determine if "ABP1" is an alternate abbreviation for the gene with HGNC ID HGNC:80 (AOC1, amine oxidase copper containing 1). The text does not mention ABP1, AOC1, or amine oxidase copper containing 1. The text appears to be about HSP110 and its interactions with chromatin remodeling complexes. Without any relevant information about the gene in question, I cannot classify ABP1 as an alternate abbreviation.
+          <t>Based on the provided text, I cannot find any evidence that the alias symbol ABP1 is an alternate abbreviation for the gene AOC1 (amine oxidase copper containing 1). The text does not mention ABP1 or AOC1 at all. Therefore, I cannot classify this as an alternate abbreviation.
 {
 "pmid": "40498025",
 "alias_symbol": "ABP1",
@@ -8352,12 +8662,13 @@
       <c r="W20" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -8372,25 +8683,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -8430,7 +8748,7 @@
 To extend our investigation of the nuclear functions of HSP110, we analyzed the HSP110–nuclear interactome by ESI-TRAP mass spectrometry. The nuclear translocation of HSP110 was induced by treating cells with the alkylating agent temozolomide at 200 µM (TZM), which induced the phosphorylation of ATR within 24 h of treatment (Figure 1a). We observed a rapid induction of HSP110 protein expression in both the cytoplasm and the nucleus. While the cytoplasmic expression of HSP110 decreased after 24 h, the nuclear expression remained high (Figure 1b,c). HSP110 was immunoprecipitated from the nuclear enriched fraction in the untreated and TMZ-treated cells (Figure 1d), and HSP110 partners were identified by mass spectrometric analysis. As expected, the number of hits was higher in the treated cell samples than in the untreated cells (Figure 1e,Table 1). We detected HSP70, in accord with the well-reported function of HSP110 as an HSP70 cofactor, and DNA-PKcs, in accord with the published role of HSP110 in the NHEJ DNA repair pathway [6]. Histones H2A, H4 and H3.1; several RNA-binding proteins; the transcription factors DDX9 and eEF-1α; and different GTPases were also detected. We found a strong enrichment of components of the chromatin remodeler SWI/SNF complexes. Five subunits of theses complexes were detected with a higher probability of interaction in the treated cells. They include the ATPase catalytic subunit SMARCA4, the core subunits SMARCC2 and SMARCB1 and the accessory proteins SMARCE1 and PBRM1 (Table 1).
 Salt gradient fractionation of chromatin demonstrated that TMZ (Figure 2a,b) and oxaliplatin (Figure 2c) treatment induced a strong enrichment of HSP110 in the chromatin-enriched fractions. As a control, SMARCC2, which is an important structural subunit of the SWI/SNF complex, and histone H3 were detected in the chromatin-enriched fraction in both control and DNA-damaged cells. Inhibiting ATR did not interfere with the association of SMARCC2 with chromatin but prevented the recruitment of HSP110 to chromatin (Figure 2d), suggesting that this event depends on DNA damage. On the other hand, inhibition of SMARCA4 did not affect the recruitment of HSP110 to the chromatin, demonstrating a SWI/SNF complex activity-independent process. Altogether, these results suggest that TMZ- or oxaliplatin-induced DNA damage promotes the association of HSP110 with chromatin.
 We confirmed that SMARCC2 and SMARCA4 are partners of HSP110 in co-precipitation experiments. SMARCA4 and SMARCC2 can co-precipitate with HSP110 (Figure 3a), and inversely, HSP110 can co-precipitate with SMARCA4 and SMARCC2 (Figure 3b). However, while recombinant human HSP110 can directly bind SMARCC2, it cannot bind to SMARCA4 (Figure 3c). The PLA assay demonstrated a strong proximity of endogenous HSP110 with SMARCC2 in oxaliplatin-treated SW480 cells (Figure 3d). Silencing of SMARCA4 did not modify the quantity of HSP110 that binds to the chromatin, confirming the SMARCA4-independent mechanism observed inFigure 2d. However, silencing of SMARCC2 decreased the enrichment of HSP110 into chromatin-bound fractions (Figure 3e), suggesting that the recruitment of HSP110 into the chromatin at least partly depends on SMARCC2.
-    Response: Based on the provided text, I cannot determine if "ABP1" is an alternate abbreviation for the gene with HGNC ID HGNC:80 (AOC1, amine oxidase copper containing 1). The text does not mention ABP1, AOC1, or amine oxidase copper containing 1. The text appears to be about HSP110 and its interactions with chromatin remodeling complexes. Without any relevant information about the gene in question, I cannot classify ABP1 as an alternate abbreviation.
+    Response: Based on the provided text, I cannot find any evidence that the alias symbol ABP1 is an alternate abbreviation for the gene AOC1 (amine oxidase copper containing 1). The text does not mention ABP1 or AOC1 at all. Therefore, I cannot classify this as an alternate abbreviation.
 {
 "pmid": "40498025",
 "alias_symbol": "ABP1",
@@ -8446,9 +8764,7 @@
       <c r="X20" t="inlineStr">
         <is>
           <t>Rating: 3
-The response is excellent and correctly follows the instructions provided. It accurately determines that the given text does not contain any information relevant to classifying "ABP1" as an alternate abbreviation for the gene AOC1 (HGNC:80). The response correctly states that the text is about HSP110 and its interactions with chromatin remodeling complexes, and does not mention ABP1, AOC1, or amine oxidase copper containing 1.
-The output is provided in the requested JSON format, with all required fields present. The "alternate_abbreviation" field is correctly set to "FALSE" since there is no evidence in the text to support it being an alternate abbreviation. The "evidence" field is appropriately left empty as there is no relevant evidence in the text.
-This response demonstrates a thorough understanding of the task and provides the correct output based on the given information and instructions.</t>
+The response is excellent. It correctly states that there is no evidence in the given text to support ABP1 being an alternate abbreviation for AOC1. The response accurately notes that neither ABP1 nor AOC1 are mentioned in the provided text at all. The answer follows the given format, providing a JSON object with the correct fields and values, including setting "alternate_abbreviation" to "FALSE" and leaving the "evidence" field empty as instructed when there is no supporting evidence. This response fully and correctly answers the original prompt.</t>
         </is>
       </c>
     </row>
@@ -8614,25 +8930,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -8687,8 +9010,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Based on my analysis of the provided text, there is no evidence that the alias symbol "GB3S" is explicitly used as an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses Gb3 (globotriaosylceramide) lipids and sphingolipids, but does not mention the A4GALT gene or use GB3S as an abbreviation for it. Therefore, I cannot conclude that GB3S is being used as an alternate abbreviation for A4GALT in this context.
-Here is the JSON output:
+          <t>Based on the provided text, there is no evidence that the alias symbol "GB3S" is an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses Gb3 (globotriaosylceramide) lipids and their interactions with Shiga toxin, but does not mention the A4GALT gene or any alternate abbreviations for it. Therefore, I cannot conclude that GB3S is an alternate abbreviation in this context.
 {
 "pmid": "32948883",
 "alias_symbol": "GB3S",
@@ -8702,12 +9024,13 @@
       <c r="W21" t="inlineStr">
         <is>
           <t xml:space="preserve">You will be given the original prompt and then the response.
-    Your task is to provide a 'rating' scoring how well the response answers the original prompt.
+    Your task is to provide a 'rating' scoring if the response answers the original prompt correctly.
     Give your answer on a scale of 1 to 3, where 1 means that the response is not helpful at all, and 3 means that the system_answer completely and correctly.
+    An alternate abbreviation is when an alias symbol represents the same gene name as the primary gene symbol but with different letters
     Here is the scale you should use to build your answer:
-    1: The response is terrible: completely irrelevant to the question asked, or very partial
-    2: The response is mediocre: answers the question, but is incorrect
-    3: The response is excellent: the correct answer to the question
+    1: The response is terrible: completely irrelevant to the question asked, or very partial, does not state whether it is an alternate abbreviation
+    2: The response is mediocre: answers the question, states whether it is an alternate abbreviation or not, but is incorrect
+    3: The response is excellent: the correct answer to the question, correctly states whether it is an alternate abbreviation or not
     Provide your feedback as follows:
     Rating: (your rating, as a number between 1 and 3)
     You MUST provide a value for 'Rating:' in your answer.
@@ -8722,25 +9045,32 @@
     Task:
     Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
     as an alternate abbreviation of the official HGNC gene symbol.
-    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    Classify the alias symbol as an Alternate Abbreviation only if it is expanded in the text to the official
     HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
     The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
-    The text must explicitly link the alias symbol to the official gene name through an expansion 
-    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    The text must link the alias symbol to the official gene name through an expansion.
     Examples:
     1-
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
-    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
-    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Official HGNC gene name: alpha-1-B glycoprotein
-    Primary gene symbol: A1BG
+    Text: “A 64-kDa human protein, cloned and identified as either ACF (APOBEC-1complementation factor) (8) or 
+    ASP (APOBEC-1 stimulating protein) (9), together with APOBEC-1 function as a minimal editosome in vitro.”
+    Reasoning: ACF64 and ACF65 are used like this "ACF64/ACF65" in the text and therefore it can be assumed that
+    this sentence is also applicable to ACF65.
+    Alias gene symbol: ACF65
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     2-
     Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
     cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Reasoning: ASP is represented by APOBEC-1 stimulating protein where stimulating is a synonym for complementation
     Alias gene symbol: ASP
     Official HGNC gene name: APOBEC1 complementation factor
     Primary gene symbol: A1CF
+    3-
+    Text: In the abbreviations section “α4GnT α1,4-N-acetylglucosaminyltransferase”
+    Reasoning: ALPHA4GNT is the same as A4GNT but with the term alpha spelled out instead of just shortened to an A
+    Alias gene symbol: ALPHA4GNT
+    Official HGNC gene name: alpha-1,4-N-acetylglucosaminyltransferase
+    Primary gene symbol: A4GNT
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "FALSE"
@@ -8791,8 +9121,7 @@
 Springer Nature remains neutral with regard to jurisdictional claims in published maps and institutional affiliations.
 The authors are grateful to the DFG (SFB 803, project A05) for financial support. C.S. thanks Ole M. Schütte, Loan Vuong, Fangyuan Li, and Jutta Gerber Nolte for their experimental work. D. B. W. thanks Annika Ries, Lukas J. Patalag and Katharina Kettelhoit for their synthetic efforts. Open Access funding provided by Projekt DEAL.
 The authors declare no conflict of interest.
-    Response: Based on my analysis of the provided text, there is no evidence that the alias symbol "GB3S" is explicitly used as an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses Gb3 (globotriaosylceramide) lipids and sphingolipids, but does not mention the A4GALT gene or use GB3S as an abbreviation for it. Therefore, I cannot conclude that GB3S is being used as an alternate abbreviation for A4GALT in this context.
-Here is the JSON output:
+    Response: Based on the provided text, there is no evidence that the alias symbol "GB3S" is an alternate abbreviation for the official gene name "alpha 1,4-galactosyltransferase (P1PK blood group)" or the primary gene symbol "A4GALT". The text discusses Gb3 (globotriaosylceramide) lipids and their interactions with Shiga toxin, but does not mention the A4GALT gene or any alternate abbreviations for it. Therefore, I cannot conclude that GB3S is an alternate abbreviation in this context.
 {
 "pmid": "32948883",
 "alias_symbol": "GB3S",
@@ -8808,12 +9137,7 @@
       <c r="X21" t="inlineStr">
         <is>
           <t>Rating: 3
-The response correctly analyzes the given text and concludes that there is no evidence of "GB3S" being used as an alternate abbreviation for the official gene name or primary gene symbol. The response follows the instructions precisely by:
-1. Examining the text for explicit links between the alias symbol and the official gene name.
-2. Correctly determining that the text does not support the alias as an alternate abbreviation.
-3. Providing the requested JSON output with the correct "alternate_abbreviation": "FALSE" and empty evidence field.
-4. Not inferring any relationships or paraphrasing evidence that isn't present.
-The response is thorough and accurate, demonstrating excellent adherence to the given task and rules. Therefore, it deserves the highest rating of 3.</t>
+The response is excellent. It correctly identifies that there is no evidence in the given text to support "GB3S" as an alternate abbreviation for the A4GALT gene or its official name. The response accurately states that the text discusses Gb3 lipids and their interactions with Shiga toxin, but does not mention the A4GALT gene or any alternate abbreviations for it. The JSON output is correctly formatted and includes all required fields, with "alternate_abbreviation" set to "FALSE" and no evidence provided, which is appropriate given the lack of relevant information in the text. This response demonstrates a thorough understanding of the task and proper application of the given rules.</t>
         </is>
       </c>
     </row>
